--- a/simulations/AO_hydrogen_peroxide_real/mass_flow_data_AO_real.xlsx
+++ b/simulations/AO_hydrogen_peroxide_real/mass_flow_data_AO_real.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AO_real\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AO_hydrogen_peroxide_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A93C3-86F6-4E7F-898F-B0435135B774}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE077E16-F727-4124-9FD6-BD143B7A590E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material streams" sheetId="1" r:id="rId1"/>
